--- a/ARM Functions/Item Edits/Mega Stone Rocky Helmet.xlsx
+++ b/ARM Functions/Item Edits/Mega Stone Rocky Helmet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Item Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D808E0-7D03-4CCD-B980-4D5894A28169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9906FF87-62F1-47EF-9B6E-769B508E14D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{6B563214-6527-4E5F-B5EA-E821D6DED3A7}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>notes</t>
   </si>
@@ -102,12 +102,6 @@
     <t>bl 0x00092298</t>
   </si>
   <si>
-    <t>ldrh r0, [r0, 0xC]</t>
-  </si>
-  <si>
-    <t>BC00D0E1</t>
-  </si>
-  <si>
     <t>Rocky Helmet 0x60</t>
   </si>
   <si>
@@ -126,27 +120,9 @@
     <t>get species</t>
   </si>
   <si>
-    <t>Table of Rocky Helmet</t>
-  </si>
-  <si>
     <t>get table</t>
   </si>
   <si>
-    <t>mov r2, 0x0</t>
-  </si>
-  <si>
-    <t>ldrh r3, [r1, r2]</t>
-  </si>
-  <si>
-    <t>cmp r0, r3</t>
-  </si>
-  <si>
-    <t>cmp r0, 0x0</t>
-  </si>
-  <si>
-    <t>add r2, r2, 0x2</t>
-  </si>
-  <si>
     <t>b 0x000B9F50</t>
   </si>
   <si>
@@ -171,55 +147,28 @@
     <t>1C41FEEB</t>
   </si>
   <si>
-    <t>28109FE5</t>
-  </si>
-  <si>
-    <t>0020A0E3</t>
-  </si>
-  <si>
-    <t>B23091E1</t>
-  </si>
-  <si>
-    <t>030050E1</t>
-  </si>
-  <si>
-    <t>0300000A</t>
-  </si>
-  <si>
-    <t>000050E3</t>
-  </si>
-  <si>
-    <t>022082E2</t>
-  </si>
-  <si>
-    <t>F8FFFFEA</t>
-  </si>
-  <si>
     <t>0F40BDE8</t>
   </si>
   <si>
-    <t>3EE0FEEA</t>
-  </si>
-  <si>
     <t>0F80BDE8</t>
   </si>
   <si>
-    <t>Table</t>
-  </si>
-  <si>
-    <t>Garchomp</t>
-  </si>
-  <si>
-    <t>Sharpedo</t>
-  </si>
-  <si>
-    <t>Aerodactyl</t>
-  </si>
-  <si>
-    <t>0014AFE0</t>
-  </si>
-  <si>
-    <t>00</t>
+    <t>bl 0x000D6F98</t>
+  </si>
+  <si>
+    <t>cmp r0, 0x1</t>
+  </si>
+  <si>
+    <t>5B54FFEB</t>
+  </si>
+  <si>
+    <t>010050E3</t>
+  </si>
+  <si>
+    <t>0100001A</t>
+  </si>
+  <si>
+    <t>45E0FEEA</t>
   </si>
 </sst>
 </file>
@@ -621,7 +570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B45B0BF-76E7-4635-9005-9D6B1877FAE8}">
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="15.9"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -658,7 +607,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B3" s="2" t="str">
         <f>_xlfn.CONCAT("0",RIGHT(C3,1),"10A0E3")</f>
@@ -723,18 +672,18 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -743,25 +692,25 @@
         <v>00101E18</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="str">
-        <f t="shared" ref="A12:A27" si="1">DEC2HEX(HEX2DEC(A11)+4,8)</f>
+        <f t="shared" ref="A12:A19" si="1">DEC2HEX(HEX2DEC(A11)+4,8)</f>
         <v>00101E1C</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D12" s="5"/>
     </row>
@@ -771,7 +720,7 @@
         <v>00101E20</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>13</v>
@@ -784,13 +733,13 @@
         <v>00101E24</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -798,15 +747,14 @@
         <f t="shared" si="1"/>
         <v>00101E28</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="2" t="str">
-        <f>_xlfn.CONCAT("ldr r1, [pc, #",HEX2DEC(A27)-HEX2DEC(A15)-8,"]")</f>
-        <v>ldr r1, [pc, #40]</v>
+      <c r="B15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -815,289 +763,52 @@
         <v>00101E2C</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>35</v>
+      </c>
+      <c r="C16" s="2" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A19)</f>
+        <v>bne 0x00101E38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" s="2" t="str">
         <f t="shared" si="1"/>
         <v>00101E30</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>29</v>
+      </c>
+      <c r="C17" s="2" t="str">
+        <f>SUBSTITUTE(C10,"push","pop")</f>
+        <v>pop {r0, r1, r2, r3, lr}</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" s="2" t="str">
         <f t="shared" si="1"/>
         <v>00101E34</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>40</v>
+      <c r="B18" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>21</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" s="2" t="str">
         <f t="shared" si="1"/>
         <v>00101E38</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C19" s="2" t="str">
-        <f>_xlfn.CONCAT("beq 0x",A24)</f>
-        <v>beq 0x00101E4C</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>00101E3C</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>00101E40</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="2" t="str">
-        <f>_xlfn.CONCAT("beq 0x",A26)</f>
-        <v>beq 0x00101E54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>00101E44</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>00101E48</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="2" t="str">
-        <f>_xlfn.CONCAT("b 0x",A17)</f>
-        <v>b 0x00101E30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>00101E4C</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="2" t="str">
-        <f>SUBSTITUTE(C10,"push","pop")</f>
-        <v>pop {r0, r1, r2, r3, lr}</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>00101E50</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>00101E54</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="2" t="str">
-        <f>SUBSTITUTE(C24,"lr","pc")</f>
+        <f>SUBSTITUTE(C17,"lr","pc")</f>
         <v>pop {r0, r1, r2, r3, pc}</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>00101E58</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" s="2" t="str">
-        <f>RIGHT(E30,2)&amp;LEFT(E30,2)</f>
-        <v>BD01</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D30" s="2">
-        <v>445</v>
-      </c>
-      <c r="E30" s="2" t="str">
-        <f>DEC2HEX(D30,4)</f>
-        <v>01BD</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="2" t="str">
-        <f>DEC2HEX(HEX2DEC(A30)+2,8)</f>
-        <v>0014AFE2</v>
-      </c>
-      <c r="B31" s="2" t="str">
-        <f>RIGHT(E31,2)&amp;LEFT(E31,2)</f>
-        <v>3F01</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D31" s="2">
-        <v>319</v>
-      </c>
-      <c r="E31" s="2" t="str">
-        <f t="shared" ref="E31:E32" si="2">DEC2HEX(D31,4)</f>
-        <v>013F</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="2" t="str">
-        <f t="shared" ref="A32:A44" si="3">DEC2HEX(HEX2DEC(A31)+2,8)</f>
-        <v>0014AFE4</v>
-      </c>
-      <c r="B32" s="2" t="str">
-        <f>RIGHT(E32,2)&amp;LEFT(E32,2)</f>
-        <v>8E00</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D32" s="2">
-        <v>142</v>
-      </c>
-      <c r="E32" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>008E</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0014AFE6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0014AFE8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0014AFEA</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0014AFEC</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0014AFEE</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0014AFF0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0014AFF2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0014AFF4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0014AFF6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0014AFF8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0014AFFA</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0014AFFC</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
